--- a/device-model-indicators/磁强计_指标库_20260225.xlsx
+++ b/device-model-indicators/磁强计_指标库_20260225.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="194" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="244" uniqueCount="51">
   <si>
     <t>型号 Model</t>
   </si>
@@ -1108,81 +1108,35 @@
       <c r="A11" s="0" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="0">
-        <v>10</v>
-      </c>
+      <c r="B11" s="0"/>
       <c r="C11" s="0">
         <v>66000</v>
       </c>
       <c r="D11" s="0">
         <v>8</v>
       </c>
-      <c r="E11" s="0">
-        <v>8</v>
-      </c>
-      <c r="F11" s="0">
-        <v>8</v>
-      </c>
-      <c r="G11" s="0">
-        <v>8</v>
-      </c>
-      <c r="H11" s="0">
-        <v>0</v>
-      </c>
-      <c r="I11" s="0">
-        <v>0</v>
-      </c>
-      <c r="J11" s="0">
-        <v>0</v>
-      </c>
-      <c r="K11" s="0">
-        <v>1</v>
-      </c>
-      <c r="L11" s="0">
-        <v>0</v>
-      </c>
-      <c r="M11" s="0">
-        <v>0</v>
-      </c>
-      <c r="N11" s="0">
-        <v>0</v>
-      </c>
-      <c r="O11" s="0">
-        <v>1</v>
-      </c>
-      <c r="P11" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="0">
-        <v>0</v>
-      </c>
-      <c r="R11" s="0">
-        <v>0</v>
-      </c>
-      <c r="S11" s="0">
-        <v>1</v>
-      </c>
-      <c r="T11" s="0">
-        <v>0.050000000000000003</v>
-      </c>
-      <c r="U11" s="0">
-        <v>0.050000000000000003</v>
-      </c>
-      <c r="V11" s="0">
-        <v>0.050000000000000003</v>
-      </c>
-      <c r="W11" s="0">
-        <v>1</v>
-      </c>
-      <c r="X11" s="0">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="0">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="0">
-        <v>0.29999999999999999</v>
-      </c>
+      <c r="E11" s="0"/>
+      <c r="F11" s="0"/>
+      <c r="G11" s="0"/>
+      <c r="H11" s="0"/>
+      <c r="I11" s="0"/>
+      <c r="J11" s="0"/>
+      <c r="K11" s="0"/>
+      <c r="L11" s="0"/>
+      <c r="M11" s="0"/>
+      <c r="N11" s="0"/>
+      <c r="O11" s="0"/>
+      <c r="P11" s="0"/>
+      <c r="Q11" s="0"/>
+      <c r="R11" s="0"/>
+      <c r="S11" s="0"/>
+      <c r="T11" s="0"/>
+      <c r="U11" s="0"/>
+      <c r="V11" s="0"/>
+      <c r="W11" s="0"/>
+      <c r="X11" s="0"/>
+      <c r="Y11" s="0"/>
+      <c r="Z11" s="0"/>
       <c r="AA11" s="0">
         <v>0.11</v>
       </c>
@@ -1194,84 +1148,32 @@
       <c r="A12" s="0" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="0">
-        <v>10</v>
-      </c>
-      <c r="C12" s="0">
-        <v>65000</v>
-      </c>
-      <c r="D12" s="0">
-        <v>10</v>
-      </c>
-      <c r="E12" s="0">
-        <v>10</v>
-      </c>
-      <c r="F12" s="0">
-        <v>10</v>
-      </c>
-      <c r="G12" s="0">
-        <v>10</v>
-      </c>
-      <c r="H12" s="0">
-        <v>0</v>
-      </c>
-      <c r="I12" s="0">
-        <v>0</v>
-      </c>
-      <c r="J12" s="0">
-        <v>0</v>
-      </c>
-      <c r="K12" s="0">
-        <v>1</v>
-      </c>
-      <c r="L12" s="0">
-        <v>0</v>
-      </c>
-      <c r="M12" s="0">
-        <v>0</v>
-      </c>
-      <c r="N12" s="0">
-        <v>0</v>
-      </c>
-      <c r="O12" s="0">
-        <v>1</v>
-      </c>
-      <c r="P12" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="0">
-        <v>0</v>
-      </c>
-      <c r="R12" s="0">
-        <v>0</v>
-      </c>
-      <c r="S12" s="0">
-        <v>1</v>
-      </c>
-      <c r="T12" s="0">
-        <v>0.050000000000000003</v>
-      </c>
-      <c r="U12" s="0">
-        <v>0.050000000000000003</v>
-      </c>
-      <c r="V12" s="0">
-        <v>0.050000000000000003</v>
-      </c>
-      <c r="W12" s="0">
-        <v>1</v>
-      </c>
-      <c r="X12" s="0">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="0">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="0">
-        <v>0.5</v>
-      </c>
-      <c r="AA12" s="0">
-        <v>0.14999999999999999</v>
-      </c>
+      <c r="B12" s="0"/>
+      <c r="C12" s="0"/>
+      <c r="D12" s="0"/>
+      <c r="E12" s="0"/>
+      <c r="F12" s="0"/>
+      <c r="G12" s="0"/>
+      <c r="H12" s="0"/>
+      <c r="I12" s="0"/>
+      <c r="J12" s="0"/>
+      <c r="K12" s="0"/>
+      <c r="L12" s="0"/>
+      <c r="M12" s="0"/>
+      <c r="N12" s="0"/>
+      <c r="O12" s="0"/>
+      <c r="P12" s="0"/>
+      <c r="Q12" s="0"/>
+      <c r="R12" s="0"/>
+      <c r="S12" s="0"/>
+      <c r="T12" s="0"/>
+      <c r="U12" s="0"/>
+      <c r="V12" s="0"/>
+      <c r="W12" s="0"/>
+      <c r="X12" s="0"/>
+      <c r="Y12" s="0"/>
+      <c r="Z12" s="0"/>
+      <c r="AA12" s="0"/>
       <c r="AB12" s="0" t="s">
         <v>47</v>
       </c>

--- a/device-model-indicators/磁强计_指标库_20260225.xlsx
+++ b/device-model-indicators/磁强计_指标库_20260225.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="244" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="294" uniqueCount="53">
   <si>
     <t>型号 Model</t>
   </si>
@@ -166,6 +166,12 @@
   </si>
   <si>
     <t>LX630 equivalent</t>
+  </si>
+  <si>
+    <t>LX630MGM60k</t>
+  </si>
+  <si>
+    <t>YYMQ9MGM</t>
   </si>
 </sst>
 </file>
@@ -1106,14 +1112,14 @@
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B11" s="0"/>
       <c r="C11" s="0">
-        <v>66000</v>
+        <v>60000</v>
       </c>
       <c r="D11" s="0">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E11" s="0"/>
       <c r="F11" s="0"/>
@@ -1138,7 +1144,7 @@
       <c r="Y11" s="0"/>
       <c r="Z11" s="0"/>
       <c r="AA11" s="0">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="AB11" s="0" t="s">
         <v>50</v>
@@ -1146,7 +1152,7 @@
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B12" s="0"/>
       <c r="C12" s="0"/>
